--- a/.xlsx files/Countries by soldier count.xlsx
+++ b/.xlsx files/Countries by soldier count.xlsx
@@ -457,7 +457,7 @@
     <t>Wundry</t>
   </si>
   <si>
-    <t>lasri</t>
+    <t>Lasri</t>
   </si>
   <si>
     <t>Myla</t>
